--- a/analisis.xlsx
+++ b/analisis.xlsx
@@ -16398,7 +16398,7 @@
         </is>
       </c>
       <c r="C34" s="2702"/>
-      <c r="D34" s="1980" cm="1">
+      <c r="D34" s="1980">
         <f t="array" ref="D34">SUMPRODUCT(('PPC '!$O$11:$O$126&lt;&gt;"X")*('PPC '!$AG$11:$AG$126&gt;0)*('PPC '!$D$11:$D$126&lt;&gt;""))</f>
         <v>0</v>
       </c>
